--- a/sessions.xlsx
+++ b/sessions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>BIZFORGE — SIMULATION SESSION LOG</t>
   </si>
@@ -50,6 +50,45 @@
   </si>
   <si>
     <t>10/6/2026, 9:44:50 am</t>
+  </si>
+  <si>
+    <t>Test Company</t>
+  </si>
+  <si>
+    <t>test@ceo.com</t>
+  </si>
+  <si>
+    <t>Agriculture (Harvest Synergy)</t>
+  </si>
+  <si>
+    <t>10/6/2026, 4:20:37 pm</t>
+  </si>
+  <si>
+    <t>jkhjv</t>
+  </si>
+  <si>
+    <t>bmhvh@hvhkg.bhjk</t>
+  </si>
+  <si>
+    <t>Education (BizForge Academy)</t>
+  </si>
+  <si>
+    <t>10/6/2026, 4:38:04 pm</t>
+  </si>
+  <si>
+    <t>Unnamed Venture</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>10/6/2026, 4:42:48 pm</t>
+  </si>
+  <si>
+    <t>Restaurant (Gastro-Net)</t>
+  </si>
+  <si>
+    <t>10/6/2026, 4:44:18 pm</t>
   </si>
 </sst>
 </file>
@@ -84,7 +123,7 @@
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +143,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +193,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -490,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -567,6 +620,110 @@
         <v>12</v>
       </c>
     </row>
+    <row r="4" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="8">
+        <v>800000</v>
+      </c>
+      <c r="F4" s="7">
+        <v>2500</v>
+      </c>
+      <c r="G4" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2500</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="8">
+        <v>250000</v>
+      </c>
+      <c r="F6" s="7">
+        <v>2500</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5">
+        <v>250000</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
